--- a/input/ocha_final.xlsx
+++ b/input/ocha_final.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted.sharepoint.com/sites/IMPACTHQ-PublicServices-IMPACT-Education/Documents partages/IMPACT - Education/Education - shared folder/PiN/PiN methodology studies 2025/new_dataset_testing/input_pin2025/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://acted-my.sharepoint.com/personal/martina_vit_impact-initiatives_org/Documents/PiN_app_dev/input/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="40" documentId="8_{086AC029-0DB3-4302-88DD-54428C2B738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{D58C92A9-16AE-4AEC-BBFF-BF53673865F6}"/>
+  <xr:revisionPtr revIDLastSave="41" documentId="8_{086AC029-0DB3-4302-88DD-54428C2B738C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{2B5D245C-F564-4777-A109-883743F88E49}"/>
   <bookViews>
-    <workbookView xWindow="-40" yWindow="-40" windowWidth="19280" windowHeight="10640" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{24D09A16-471A-4A7F-BD10-C475AB78837D}"/>
   </bookViews>
   <sheets>
     <sheet name="ocha" sheetId="1" r:id="rId1"/>
@@ -903,7 +903,7 @@
       <name val="Roboto Condensed"/>
     </font>
   </fonts>
-  <fills count="10">
+  <fills count="11">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -955,6 +955,12 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="5" tint="0.59999389629810485"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.79998168889431442"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1016,7 +1022,7 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
     <xf numFmtId="164" fontId="18" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="21">
+  <cellXfs count="22">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="1" xfId="0" applyBorder="1"/>
     <xf numFmtId="0" fontId="0" fillId="7" borderId="0" xfId="0" applyFill="1"/>
@@ -1066,6 +1072,7 @@
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="19" fillId="10" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="3">
     <cellStyle name="Comma" xfId="2" builtinId="3"/>
@@ -2466,10 +2473,10 @@
       </c>
     </row>
     <row r="36" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A36" s="16" t="s">
+      <c r="A36" s="21" t="s">
         <v>25</v>
       </c>
-      <c r="B36" s="16" t="s">
+      <c r="B36" s="21" t="s">
         <v>92</v>
       </c>
       <c r="C36" s="18">
@@ -2494,10 +2501,10 @@
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A37" s="16" t="s">
+      <c r="A37" s="21" t="s">
         <v>26</v>
       </c>
-      <c r="B37" s="16" t="s">
+      <c r="B37" s="21" t="s">
         <v>93</v>
       </c>
       <c r="C37" s="18">
@@ -3716,7 +3723,22 @@
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4A1044A-A7C4-474B-90D7-000229B24865}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F4A1044A-A7C4-474B-90D7-000229B24865}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/contentType"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes"/>
+    <ds:schemaRef ds:uri="http://www.w3.org/2001/XMLSchema"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="b5940141-1bc9-4c17-b1bc-e50f6b2083d6"/>
+    <ds:schemaRef ds:uri="14cbb838-50ff-4dab-9c3f-cddf75f03c13"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="http://schemas.openxmlformats.org/package/2006/metadata/core-properties"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/elements/1.1/"/>
+    <ds:schemaRef ds:uri="http://purl.org/dc/terms/"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/internal/obd"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
